--- a/kahoot/orientation/history/9_finnish_history__0005.xlsx
+++ b/kahoot/orientation/history/9_finnish_history__0005.xlsx
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>En central roll i att trygga människors försörjning och levnadsstandard</t>
+          <t>En central roll i att trygga försörjning och levnadsstandard</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
